--- a/web/src/public/烟箱信息汇总完整版.xlsx
+++ b/web/src/public/烟箱信息汇总完整版.xlsx
@@ -1232,11 +1232,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I3" s="15" t="n"/>
       <c r="J3" s="17" t="n"/>
     </row>
     <row r="4">
@@ -1396,11 +1392,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I7" s="15" t="n"/>
       <c r="J7" s="17" t="n"/>
     </row>
     <row r="8">
@@ -1680,11 +1672,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I14" s="15" t="n"/>
       <c r="J14" s="17" t="n"/>
     </row>
     <row r="15">
@@ -1764,11 +1752,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I16" s="15" t="n"/>
       <c r="J16" s="17" t="n"/>
     </row>
     <row r="17">
@@ -1994,11 +1978,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="17" t="n"/>
     </row>
     <row r="23">
@@ -2038,11 +2018,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="17" t="n"/>
     </row>
     <row r="24">
@@ -2124,11 +2100,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I25" s="15" t="n"/>
       <c r="J25" s="17" t="n"/>
     </row>
     <row r="26">
@@ -2252,11 +2224,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I28" s="15" t="n"/>
       <c r="J28" s="17" t="n"/>
     </row>
     <row r="29">
@@ -2296,11 +2264,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I29" s="15" t="n"/>
       <c r="J29" s="10" t="inlineStr">
         <is>
           <t>更改名字为“龙烟（呈祥）”</t>
@@ -2628,11 +2592,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I37" s="15" t="n"/>
       <c r="J37" s="17" t="n"/>
     </row>
     <row r="38">
@@ -2709,7 +2669,7 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>5*6</t>
+          <t>5*8</t>
         </is>
       </c>
       <c r="I39" s="15" t="inlineStr"/>
@@ -2752,11 +2712,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I40" s="15" t="n"/>
       <c r="J40" s="17" t="n"/>
     </row>
     <row r="41">
@@ -2886,11 +2842,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="17" t="n"/>
     </row>
     <row r="45">
@@ -2930,11 +2882,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I45" s="15" t="n"/>
       <c r="J45" s="17" t="n"/>
     </row>
     <row r="46">
@@ -2974,11 +2922,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="17" t="n"/>
     </row>
     <row r="47">
@@ -3018,11 +2962,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I47" s="15" t="n"/>
       <c r="J47" s="17" t="n"/>
     </row>
     <row r="48">
@@ -3097,14 +3037,10 @@
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
           <t>5*6</t>
         </is>
       </c>
+      <c r="I49" s="15" t="n"/>
       <c r="J49" s="17" t="n"/>
     </row>
     <row r="50">
@@ -3188,11 +3124,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I51" s="15" t="n"/>
       <c r="J51" s="17" t="n"/>
     </row>
     <row r="52">
@@ -3229,7 +3161,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
+          <t>5*6</t>
         </is>
       </c>
       <c r="I52" s="15" t="n"/>
@@ -3540,11 +3472,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I60" s="15" t="n"/>
       <c r="J60" s="17" t="n"/>
     </row>
     <row r="61">
@@ -3624,11 +3552,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I62" s="15" t="n"/>
       <c r="J62" s="17" t="n"/>
     </row>
     <row r="63">
@@ -3708,11 +3632,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I64" s="15" t="n"/>
       <c r="J64" s="17" t="n"/>
     </row>
     <row r="65">
@@ -3792,11 +3712,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I66" s="15" t="n"/>
       <c r="J66" s="17" t="n"/>
     </row>
     <row r="67">
@@ -3892,11 +3808,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I69" s="15" t="n"/>
       <c r="J69" s="17" t="n"/>
     </row>
     <row r="70">
@@ -3976,11 +3888,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I71" s="15" t="n"/>
       <c r="J71" s="17" t="n"/>
     </row>
     <row r="72">
@@ -4020,11 +3928,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I72" s="15" t="n"/>
       <c r="J72" s="17" t="n"/>
     </row>
     <row r="73">
@@ -4064,11 +3968,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I73" s="15" t="n"/>
       <c r="J73" s="17" t="n"/>
     </row>
     <row r="74">
@@ -4208,11 +4108,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I77" s="15" t="n"/>
       <c r="J77" s="17" t="n"/>
     </row>
     <row r="78">
@@ -4464,11 +4360,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I84" s="15" t="n"/>
       <c r="J84" s="17" t="n"/>
     </row>
     <row r="85">
@@ -4505,14 +4397,10 @@
       </c>
       <c r="H85" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
-        </is>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
           <t>5*6</t>
         </is>
       </c>
+      <c r="I85" s="15" t="n"/>
       <c r="J85" s="17" t="n"/>
     </row>
     <row r="86">
@@ -4639,14 +4527,10 @@
       </c>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
-        </is>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
           <t>5*6</t>
         </is>
       </c>
+      <c r="I89" s="15" t="n"/>
       <c r="J89" s="17" t="n"/>
     </row>
     <row r="90">
@@ -4686,11 +4570,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I90" s="15" t="n"/>
       <c r="J90" s="17" t="n"/>
     </row>
     <row r="91">
@@ -4730,11 +4610,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I91" s="15" t="n"/>
       <c r="J91" s="17" t="n"/>
     </row>
     <row r="92">
@@ -5003,14 +4879,10 @@
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>5*6</t>
-        </is>
-      </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+          <t>特殊垛型</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="n"/>
       <c r="J99" s="17" t="n"/>
     </row>
     <row r="100">
@@ -5340,11 +5212,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I108" s="15" t="n"/>
       <c r="J108" s="17" t="n"/>
     </row>
     <row r="109">
@@ -5448,11 +5316,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I111" s="15" t="n"/>
       <c r="J111" s="17" t="n"/>
     </row>
     <row r="112">
@@ -5492,11 +5356,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I112" s="15" t="n"/>
       <c r="J112" s="17" t="n"/>
     </row>
     <row r="113">
@@ -5572,11 +5432,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I114" s="15" t="n"/>
       <c r="J114" s="17" t="n"/>
     </row>
     <row r="115">
@@ -5912,11 +5768,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I124" s="15" t="n"/>
       <c r="J124" s="17" t="n"/>
     </row>
     <row r="125">
@@ -5956,11 +5808,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I125" s="15" t="n"/>
       <c r="J125" s="17" t="n"/>
     </row>
     <row r="126">
@@ -5998,11 +5846,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I126" s="15" t="n"/>
       <c r="J126" s="17" t="inlineStr">
         <is>
           <t>按照5*6做算法</t>
@@ -6094,11 +5938,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I129" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I129" s="15" t="n"/>
       <c r="J129" s="17" t="n"/>
     </row>
     <row r="130">
@@ -6178,11 +6018,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I131" s="15" t="n"/>
       <c r="J131" s="17" t="n"/>
     </row>
     <row r="132">
@@ -6262,11 +6098,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I133" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I133" s="15" t="n"/>
       <c r="J133" s="17" t="n"/>
     </row>
     <row r="134">
@@ -6377,11 +6209,7 @@
       </c>
       <c r="F136" s="15" t="inlineStr"/>
       <c r="G136" s="15" t="inlineStr"/>
-      <c r="H136" s="15" t="inlineStr">
-        <is>
-          <t>3*10</t>
-        </is>
-      </c>
+      <c r="H136" s="15" t="n"/>
       <c r="I136" s="15" t="n"/>
       <c r="J136" s="17" t="inlineStr">
         <is>
@@ -6426,11 +6254,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I137" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I137" s="15" t="n"/>
       <c r="J137" s="10" t="inlineStr">
         <is>
           <t>更改名字为“白沙(硬天天向上细支)2”</t>
@@ -6834,11 +6658,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I148" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I148" s="15" t="n"/>
       <c r="J148" s="17" t="n"/>
     </row>
     <row r="149">
@@ -7022,11 +6842,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I153" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I153" s="15" t="n"/>
       <c r="J153" s="17" t="n"/>
     </row>
     <row r="154">
@@ -7106,11 +6922,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I155" s="15" t="n"/>
       <c r="J155" s="17" t="n"/>
     </row>
     <row r="156">
@@ -7375,14 +7187,10 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
-        </is>
-      </c>
-      <c r="I162" s="15" t="inlineStr">
-        <is>
           <t>5*6</t>
         </is>
       </c>
+      <c r="I162" s="15" t="n"/>
       <c r="J162" s="17" t="n"/>
     </row>
     <row r="163">
@@ -7662,11 +7470,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I169" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I169" s="15" t="n"/>
       <c r="J169" s="17" t="n"/>
     </row>
     <row r="170">
@@ -7746,11 +7550,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I171" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I171" s="15" t="n"/>
       <c r="J171" s="17" t="n"/>
     </row>
     <row r="172">
@@ -7910,11 +7710,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I175" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I175" s="15" t="n"/>
       <c r="J175" s="17" t="n"/>
     </row>
     <row r="176">
@@ -7954,11 +7750,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I176" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I176" s="15" t="n"/>
       <c r="J176" s="17" t="n"/>
     </row>
     <row r="177">
@@ -7995,14 +7787,10 @@
       </c>
       <c r="H177" s="15" t="inlineStr">
         <is>
-          <t>5*8</t>
-        </is>
-      </c>
-      <c r="I177" s="15" t="inlineStr">
-        <is>
           <t>5*6</t>
         </is>
       </c>
+      <c r="I177" s="15" t="n"/>
       <c r="J177" s="17" t="n"/>
     </row>
     <row r="178">
@@ -8430,11 +8218,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I188" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I188" s="15" t="n"/>
       <c r="J188" s="17" t="n"/>
     </row>
     <row r="189">
@@ -8474,11 +8258,7 @@
           <t>5*8</t>
         </is>
       </c>
-      <c r="I189" s="15" t="inlineStr">
-        <is>
-          <t>5*6</t>
-        </is>
-      </c>
+      <c r="I189" s="15" t="n"/>
       <c r="J189" s="17" t="n"/>
     </row>
     <row r="190">
@@ -8830,11 +8610,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I198" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I198" s="15" t="n"/>
       <c r="J198" s="17" t="n"/>
     </row>
     <row r="199">
@@ -8870,11 +8646,7 @@
           <t>5*6</t>
         </is>
       </c>
-      <c r="I199" s="15" t="inlineStr">
-        <is>
-          <t>5*8</t>
-        </is>
-      </c>
+      <c r="I199" s="15" t="n"/>
       <c r="J199" s="17" t="n"/>
     </row>
   </sheetData>
